--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487750_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487750_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0619</v>
+        <v>7.9717</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9064</v>
+        <v>4.7072</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1555</v>
+        <v>3.2645</v>
       </c>
       <c r="G2" t="n">
         <v>4.7165</v>
@@ -610,13 +610,13 @@
         <v>2.5224</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9098000000000001</v>
+        <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7134</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1965</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>4.6134</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.9192</v>
+        <v>5.4149</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8027</v>
+        <v>3.4619</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1166</v>
+        <v>1.953</v>
       </c>
       <c r="G3" t="n">
         <v>2.633</v>
@@ -688,13 +688,13 @@
         <v>1.9403</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4504</v>
+        <v>0.946</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0289</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4215</v>
+        <v>0.258</v>
       </c>
       <c r="V3" t="n">
         <v>1.8358</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2747</v>
+        <v>4.4988</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0962</v>
+        <v>3.1567</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1785</v>
+        <v>1.342</v>
       </c>
       <c r="G4" t="n">
         <v>2.3402</v>
@@ -766,13 +766,13 @@
         <v>1.3582</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0357</v>
+        <v>0.1884</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0348</v>
+        <v>0.0258</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0009</v>
+        <v>0.1626</v>
       </c>
       <c r="V4" t="n">
         <v>0.6119</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.686</v>
+        <v>1.4134</v>
       </c>
       <c r="E5" t="n">
         <v>-0.2018</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8878</v>
+        <v>1.6153</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2344</v>
@@ -844,13 +844,13 @@
         <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4845</v>
+        <v>0.212</v>
       </c>
       <c r="T5" t="n">
         <v>0.1222</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3623</v>
+        <v>0.0897</v>
       </c>
       <c r="V5" t="n">
         <v>0.6597</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6774</v>
+        <v>1.0867</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.073</v>
+        <v>-1.7727</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7504</v>
+        <v>2.8594</v>
       </c>
       <c r="G6" t="n">
         <v>-1.7237</v>
@@ -922,13 +922,13 @@
         <v>2.7164</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3154</v>
+        <v>0.0939</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.046</v>
+        <v>0.2543</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2694</v>
+        <v>-0.1603</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0412</v>
+        <v>-0.162</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8642</v>
+        <v>-2.203</v>
       </c>
       <c r="F7" t="n">
-        <v>1.823</v>
+        <v>2.041</v>
       </c>
       <c r="G7" t="n">
         <v>-4.7654</v>
@@ -1000,13 +1000,13 @@
         <v>1.7463</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7519</v>
+        <v>0.1273</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5193</v>
+        <v>0.1418</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2326</v>
+        <v>-0.0145</v>
       </c>
       <c r="V7" t="n">
         <v>2.7298</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1071</v>
+        <v>-1.4108</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0854</v>
+        <v>-1.5253</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0217</v>
+        <v>0.1145</v>
       </c>
       <c r="G8" t="n">
         <v>-2.7513</v>
@@ -1078,13 +1078,13 @@
         <v>0.7761</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8681</v>
+        <v>0.5644</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8142</v>
+        <v>0.3743</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0538</v>
+        <v>0.1901</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4121</v>
+        <v>-2.2119</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2919</v>
+        <v>-2.0917</v>
       </c>
       <c r="F9" t="n">
         <v>-0.1202</v>
@@ -1156,10 +1156,10 @@
         <v>0.7761</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0123</v>
+        <v>0.2125</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0482</v>
+        <v>0.152</v>
       </c>
       <c r="U9" t="n">
         <v>0.0606</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0632</v>
+        <v>-3.6628</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6994</v>
+        <v>-2.299</v>
       </c>
       <c r="F10" t="n">
         <v>-1.3639</v>
@@ -1234,10 +1234,10 @@
         <v>1.7463</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1211</v>
+        <v>0.2793</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0134</v>
+        <v>0.4138</v>
       </c>
       <c r="U10" t="n">
         <v>-0.1346</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. SCHUCH</t>
+          <t>T. VERDERA BENASSAR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8544</v>
+        <v>-5.2728</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.7668</v>
+        <v>-6.7217</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9125</v>
+        <v>1.4489</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.8652</v>
+        <v>-4.474</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7209</v>
+        <v>-2.2006</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.1443</v>
+        <v>-2.2734</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.1246</v>
+        <v>-3.7386</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8692</v>
+        <v>-2.5663</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.2555</v>
+        <v>-1.1723</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2595</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1483</v>
+        <v>0.3658</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1112</v>
+        <v>-1.1011</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.8806</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.8508</v>
+        <v>-2.9105</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9702</v>
+        <v>2.1344</v>
       </c>
       <c r="S11" t="n">
-        <v>1.8914</v>
+        <v>0.355</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9847</v>
+        <v>0.305</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9067</v>
+        <v>0.0499</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.3776</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2239</v>
+        <v>-0.3776</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. VERDERA BENASSAR</t>
+          <t>B. SCHUCH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8639</v>
+        <v>-7.0852</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.1221</v>
+        <v>-7.5071</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2581</v>
+        <v>0.4219</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.474</v>
+        <v>-3.8652</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.2006</v>
+        <v>-0.7209</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2734</v>
+        <v>-3.1443</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.7386</v>
+        <v>-4.1246</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.5663</v>
+        <v>-0.8692</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1723</v>
+        <v>-3.2555</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7354000000000001</v>
+        <v>0.2595</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3658</v>
+        <v>0.1483</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1011</v>
+        <v>0.1112</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7761</v>
+        <v>-3.8806</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9105</v>
+        <v>-4.8508</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1344</v>
+        <v>0.9702</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2362</v>
+        <v>0.6606</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0954</v>
+        <v>0.2445</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1408</v>
+        <v>0.4161</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3776</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3776</v>
+        <v>1.2239</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="13">
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2773000000000012</v>
+        <v>0.5799999999999983</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.2993</v>
+        <v>-12.9965</v>
       </c>
       <c r="F13" t="n">
-        <v>13.5766</v>
+        <v>13.5764</v>
       </c>
       <c r="G13" t="n">
         <v>-13.8207</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.0339</v>
+        <v>-5.033900000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.786800000000001</v>
+        <v>-8.786799999999999</v>
       </c>
       <c r="J13" t="n">
         <v>-11.0785</v>
@@ -1459,7 +1459,7 @@
         <v>-4.2824</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9702000000000002</v>
+        <v>0.9701999999999997</v>
       </c>
       <c r="Q13" t="n">
         <v>-16.4927</v>
@@ -1468,13 +1468,13 @@
         <v>17.4628</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3366</v>
+        <v>3.6394</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5063</v>
+        <v>2.8091</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.8301999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>9.790900000000002</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2311</v>
+        <v>3.8814</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8247</v>
+        <v>1.4233</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4064</v>
+        <v>2.4581</v>
       </c>
       <c r="G14" t="n">
         <v>3.2354</v>
@@ -1546,13 +1546,13 @@
         <v>2.1344</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8017</v>
+        <v>0.452</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5186</v>
+        <v>0.1172</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2831</v>
+        <v>0.3348</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2077</v>
+        <v>3.0019</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0762</v>
+        <v>2.876</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1315</v>
+        <v>0.1259</v>
       </c>
       <c r="G15" t="n">
         <v>5.2301</v>
@@ -1624,13 +1624,13 @@
         <v>1.5523</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1447</v>
+        <v>-0.0611</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1839</v>
+        <v>-0.0163</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0392</v>
+        <v>-0.0448</v>
       </c>
       <c r="V15" t="n">
         <v>-3.7194</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>N. MAIGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5757</v>
+        <v>2.7857</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4979</v>
+        <v>-0.6613</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0778</v>
+        <v>3.447</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6233</v>
+        <v>3.1712</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1845</v>
+        <v>2.9165</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8078</v>
+        <v>0.2547</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4957</v>
+        <v>1.4436</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9886</v>
+        <v>2.1009</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4843</v>
+        <v>-0.6573</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1276</v>
+        <v>1.7276</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8041</v>
+        <v>0.8156</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3235</v>
+        <v>0.912</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1344</v>
+        <v>-0.194</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1344</v>
+        <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2658</v>
+        <v>-0.1915</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0022</v>
+        <v>-0.1646</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2636</v>
+        <v>-0.0269</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. MAIGA</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1517</v>
+        <v>2.7036</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1618</v>
+        <v>0.4979</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3135</v>
+        <v>2.2057</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1712</v>
+        <v>2.6233</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9165</v>
+        <v>-0.1845</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2547</v>
+        <v>2.8078</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4436</v>
+        <v>0.4957</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1009</v>
+        <v>-0.9886</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6573</v>
+        <v>1.4843</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7276</v>
+        <v>2.1276</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8156</v>
+        <v>0.8041</v>
       </c>
       <c r="O17" t="n">
-        <v>0.912</v>
+        <v>1.3235</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.194</v>
+        <v>2.1344</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7463</v>
+        <v>2.1344</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8255</v>
+        <v>0.3937</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6651</v>
+        <v>0.0022</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1603</v>
+        <v>0.3915</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. LARDIES GUILLEN</t>
+          <t>H. PEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2855</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1817</v>
+        <v>-1.2104</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4672</v>
+        <v>1.7452</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1944</v>
+        <v>0.3353</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.206</v>
+        <v>0.318</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4004</v>
+        <v>0.0172</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.6198</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.0247</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.6445</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1944</v>
+        <v>0.955</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.206</v>
+        <v>0.2933</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4004</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R18" t="n">
-        <v>0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.103</v>
+        <v>-0.0541</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1817</v>
+        <v>0.1259</v>
       </c>
       <c r="U18" t="n">
-        <v>0.07870000000000001</v>
+        <v>-0.18</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. PEREZ SANCHEZ</t>
+          <t>R. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.244</v>
+        <v>0.4129</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9101</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>1.154</v>
+        <v>0.4945</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3353</v>
+        <v>0.1944</v>
       </c>
       <c r="H19" t="n">
-        <v>0.318</v>
+        <v>-0.206</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0172</v>
+        <v>0.4004</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6198</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0247</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6445</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.955</v>
+        <v>0.1944</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2933</v>
+        <v>-0.206</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.4004</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9702</v>
+        <v>0.194</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9702</v>
+        <v>0.194</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.345</v>
+        <v>0.0244</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4262</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7712</v>
+        <v>0.106</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>D. FERNANDEZ CAÑAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9604</v>
+        <v>-0.6821</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5324</v>
+        <v>-3.26</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4928</v>
+        <v>2.5779</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1862</v>
+        <v>1.8832</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9771</v>
+        <v>1.5406</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2091</v>
+        <v>0.3426</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4025</v>
+        <v>-0.2236</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3213</v>
+        <v>0.3625</v>
       </c>
       <c r="L20" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.5861</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7837</v>
+        <v>2.1068</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6558</v>
+        <v>1.1781</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1279</v>
+        <v>0.9287</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7761</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4668</v>
+        <v>-0.625</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7896</v>
+        <v>-0.408</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3228</v>
+        <v>-0.217</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.3895</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6597</v>
+        <v>0.2821</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.7298</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CAÑAS</t>
+          <t>J. DOMINGUEZ LARRE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3133</v>
+        <v>-1.3278</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7605</v>
+        <v>-3.8652</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4472</v>
+        <v>2.5374</v>
       </c>
       <c r="G21" t="n">
-        <v>1.8832</v>
+        <v>0.1429</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5406</v>
+        <v>-0.5289</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3426</v>
+        <v>0.6718</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2236</v>
+        <v>-0.6504</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3625</v>
+        <v>-1.2111</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5861</v>
+        <v>0.5606</v>
       </c>
       <c r="M21" t="n">
-        <v>2.1068</v>
+        <v>0.7933</v>
       </c>
       <c r="N21" t="n">
-        <v>1.1781</v>
+        <v>0.6821</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9287</v>
+        <v>0.1112</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.9403</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.9105</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9702</v>
+        <v>1.7463</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2561</v>
+        <v>-0.0244</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9085</v>
+        <v>-0.3043</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3477</v>
+        <v>0.2799</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>-0.2821</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ LARRE</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8433</v>
+        <v>-1.4016</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1655</v>
+        <v>-1.8949</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3222</v>
+        <v>0.4933</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1429</v>
+        <v>-0.9234</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5289</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6718</v>
+        <v>-1.566</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6504</v>
+        <v>-1.0323</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2111</v>
+        <v>0.239</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5606</v>
+        <v>-1.2712</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7933</v>
+        <v>0.1089</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6821</v>
+        <v>0.4037</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1112</v>
+        <v>-0.2948</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1642</v>
+        <v>0.3881</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7463</v>
+        <v>2.3284</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5399</v>
+        <v>-0.2543</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6046</v>
+        <v>-0.1461</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0646</v>
+        <v>-0.1082</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2821</v>
+        <v>-0.6119</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2821</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4265</v>
+        <v>-1.6728</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5956</v>
+        <v>-0.0682</v>
       </c>
       <c r="F23" t="n">
-        <v>0.169</v>
+        <v>-1.6046</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9234</v>
+        <v>1.1862</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.9771</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.566</v>
+        <v>0.2091</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0323</v>
+        <v>0.4025</v>
       </c>
       <c r="K23" t="n">
-        <v>0.239</v>
+        <v>0.3213</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2712</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1089</v>
+        <v>0.7837</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4037</v>
+        <v>0.6558</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2948</v>
+        <v>0.1279</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3284</v>
+        <v>0.7761</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2793</v>
+        <v>-0.2456</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8468</v>
+        <v>0.189</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4324</v>
+        <v>-0.4346</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6119</v>
+        <v>-3.3895</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2239</v>
+        <v>-0.6597</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.8358</v>
+        <v>-2.7298</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0597</v>
+        <v>-2.3957</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1122</v>
+        <v>-2.6117</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0525</v>
+        <v>0.216</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8351</v>
@@ -2326,13 +2326,13 @@
         <v>0.5821</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8365</v>
+        <v>-0.1724</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5451</v>
+        <v>-0.0446</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2914</v>
+        <v>-0.1278</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.3697</v>
+        <v>-4.1155</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.6204</v>
+        <v>-4.7205</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2506</v>
+        <v>0.605</v>
       </c>
       <c r="G25" t="n">
         <v>-1.4229</v>
@@ -2404,13 +2404,13 @@
         <v>1.3582</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8304</v>
+        <v>-0.5762</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0011</v>
+        <v>-0.099</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8315</v>
+        <v>-0.4772</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5642</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2771999999999988</v>
+        <v>1.724799999999999</v>
       </c>
       <c r="E26" t="n">
         <v>-13.5766</v>
       </c>
       <c r="F26" t="n">
-        <v>13.2991</v>
+        <v>15.3014</v>
       </c>
       <c r="G26" t="n">
         <v>13.8206</v>
@@ -2455,7 +2455,7 @@
         <v>8.7866</v>
       </c>
       <c r="J26" t="n">
-        <v>2.742100000000001</v>
+        <v>2.742099999999999</v>
       </c>
       <c r="K26" t="n">
         <v>-1.5405</v>
@@ -2473,7 +2473,7 @@
         <v>4.504300000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.9701999999999997</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q26" t="n">
         <v>-17.4629</v>
@@ -2482,16 +2482,16 @@
         <v>16.4929</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.3367</v>
+        <v>-1.3345</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8302000000000003</v>
+        <v>-0.8301999999999998</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.5065</v>
+        <v>-0.5042999999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>-9.790899999999999</v>
+        <v>-9.790900000000001</v>
       </c>
       <c r="W26" t="n">
         <v>1.9747</v>
